--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="焊缝统计" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常报告" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="焊缝统计" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="异常报告" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
         <v>250</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
         <v>250</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>116.4</v>
+        <v>231.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>116.4</v>
+        <v>231.4</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>220.9</v>
+        <v>438.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>220.9</v>
+        <v>438.9</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D81" t="n">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -3059,14 +3059,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C82" t="n">
+        <v>6</v>
+      </c>
       <c r="D82" t="n">
-        <v>268</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3074,7 +3073,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3093,10 +3092,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
@@ -3106,7 +3105,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3124,22 +3123,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C84" t="n">
+        <v>7</v>
+      </c>
       <c r="D84" t="n">
-        <v>218</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3158,20 +3156,20 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3190,10 +3188,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
@@ -3203,7 +3201,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3222,10 +3220,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
@@ -3235,7 +3233,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3257,17 +3255,17 @@
         <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>p18</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>p19</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3289,17 +3287,17 @@
         <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>p18</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>p19</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3321,17 +3319,17 @@
         <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3353,17 +3351,17 @@
         <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3385,7 +3383,7 @@
         <v>7</v>
       </c>
       <c r="D92" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
@@ -3417,7 +3415,7 @@
         <v>7</v>
       </c>
       <c r="D93" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -3449,17 +3447,17 @@
         <v>7</v>
       </c>
       <c r="D94" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>p18</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>p19</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -3481,17 +3479,17 @@
         <v>7</v>
       </c>
       <c r="D95" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
+          <t>BE022</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>p18</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>p19</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3509,13 +3507,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>7</v>
-      </c>
       <c r="D96" t="n">
-        <v>120</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
+        <v>438.9</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3523,7 +3522,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3545,7 +3544,7 @@
         <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>120</v>
+        <v>438.9</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
@@ -3555,7 +3554,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3573,13 +3572,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>7</v>
-      </c>
       <c r="D98" t="n">
-        <v>29</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
+        <v>231.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
           <t>BE022</t>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3609,7 +3609,7 @@
         <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>29</v>
+        <v>231.4</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p200</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D101" t="n">
-        <v>218</v>
+        <v>268</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
@@ -3702,27 +3702,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C102" t="n">
+        <v>9</v>
+      </c>
       <c r="D102" t="n">
-        <v>115</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3736,25 +3735,25 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>115</v>
+        <v>440</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3767,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3777,7 +3776,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3787,7 +3786,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3801,15 +3800,15 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3819,7 +3818,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3832,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>116.4</v>
+        <v>140</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3842,7 +3841,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3852,7 +3851,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3866,15 +3865,15 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>116.4</v>
+        <v>140</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3884,7 +3883,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3897,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>220.9</v>
+        <v>268</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3907,7 +3906,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3917,7 +3916,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3931,15 +3930,15 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>220.9</v>
+        <v>268</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -3949,7 +3948,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>BE022</t>
+          <t>BE023</t>
         </is>
       </c>
     </row>
@@ -3963,10 +3962,10 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
-        <v>419</v>
+        <v>140</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
@@ -3976,7 +3975,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -3995,10 +3994,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>419</v>
+        <v>140</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
@@ -4008,7 +4007,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4027,7 +4026,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>116.4</v>
+        <v>140</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4060,10 +4059,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>116.4</v>
+        <v>140</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
@@ -4092,7 +4091,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>220.9</v>
+        <v>140</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4125,10 +4124,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>220.9</v>
+        <v>140</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
@@ -4157,7 +4156,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4190,10 +4189,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D117" t="n">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
@@ -4221,22 +4220,21 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C118" t="n">
+        <v>7</v>
+      </c>
       <c r="D118" t="n">
-        <v>268</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4255,20 +4253,20 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4286,14 +4284,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C120" t="n">
+        <v>7</v>
+      </c>
       <c r="D120" t="n">
-        <v>218</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>BE023</t>
@@ -4301,7 +4298,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4320,10 +4317,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
@@ -4333,7 +4330,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4352,10 +4349,10 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D122" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
@@ -4365,7 +4362,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -4384,10 +4381,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D123" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
@@ -4397,7 +4394,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4415,27 +4412,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C124" t="n">
+        <v>7</v>
+      </c>
       <c r="D124" t="n">
-        <v>218</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>134.4</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4449,25 +4445,25 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D125" t="n">
-        <v>218</v>
+        <v>134.4</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4480,27 +4476,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C126" t="n">
+        <v>7</v>
+      </c>
       <c r="D126" t="n">
-        <v>115</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4514,25 +4509,25 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4545,27 +4540,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C128" t="n">
+        <v>7</v>
+      </c>
       <c r="D128" t="n">
         <v>268</v>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4573,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D129" t="n">
         <v>268</v>
@@ -4587,17 +4581,17 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4610,27 +4604,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C130" t="n">
+        <v>7</v>
+      </c>
       <c r="D130" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4644,25 +4637,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
-        <v>116.4</v>
+        <v>90.5</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4672,30 +4665,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>7</v>
       </c>
       <c r="D132" t="n">
-        <v>220.9</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4705,29 +4697,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
-        <v>220.9</v>
+        <v>90.5</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>p200</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4737,29 +4729,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C134" t="n">
         <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>120</v>
+        <v>90.5</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4769,29 +4761,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4801,29 +4793,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>7</v>
       </c>
       <c r="D136" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4833,29 +4825,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4865,29 +4857,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>7</v>
       </c>
       <c r="D138" t="n">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4897,29 +4889,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>BE023</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -4929,14 +4921,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>134.4</v>
+        <v>60</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -4946,7 +4938,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -4961,24 +4953,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>134.4</v>
+        <v>110</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -4993,24 +4985,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C142" t="n">
         <v>7</v>
       </c>
       <c r="D142" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5025,14 +5017,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
@@ -5042,7 +5034,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5057,14 +5049,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
-        <v>268</v>
+        <v>90.5</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
@@ -5074,7 +5066,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5089,14 +5081,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>7</v>
       </c>
       <c r="D145" t="n">
-        <v>268</v>
+        <v>50</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
@@ -5106,7 +5098,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5121,14 +5113,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C146" t="n">
         <v>7</v>
       </c>
       <c r="D146" t="n">
-        <v>90.5</v>
+        <v>50</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
@@ -5138,7 +5130,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5153,11 +5145,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D147" t="n">
         <v>90.5</v>
@@ -5170,7 +5162,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5189,20 +5181,20 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D148" t="n">
-        <v>172</v>
+        <v>90.5</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5220,13 +5212,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>7</v>
-      </c>
       <c r="D149" t="n">
         <v>90.5</v>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5234,7 +5227,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -5249,16 +5242,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D150" t="n">
         <v>90.5</v>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5266,7 +5260,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5281,14 +5275,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D151" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
@@ -5298,7 +5292,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5317,10 +5311,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D152" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
@@ -5330,7 +5324,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5348,13 +5342,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>7</v>
-      </c>
       <c r="D153" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E153" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5362,7 +5357,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5377,16 +5372,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D154" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E154" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5394,7 +5390,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5409,14 +5405,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
@@ -5426,7 +5422,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -5445,10 +5441,10 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D156" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
@@ -5458,7 +5454,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5476,21 +5472,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>7</v>
-      </c>
       <c r="D157" t="n">
         <v>90.5</v>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5505,24 +5502,25 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D158" t="n">
         <v>90.5</v>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -5537,11 +5535,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D159" t="n">
         <v>90.5</v>
@@ -5554,7 +5552,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -5573,7 +5571,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D160" t="n">
         <v>90.5</v>
@@ -5586,7 +5584,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -5608,22 +5606,22 @@
         <v>7</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>313</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5640,22 +5638,22 @@
         <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>50</v>
+        <v>313</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5669,25 +5667,25 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D163" t="n">
-        <v>90.5</v>
+        <v>313</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5701,25 +5699,25 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D164" t="n">
-        <v>90.5</v>
+        <v>313</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5732,27 +5730,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C165" t="n">
+        <v>7</v>
+      </c>
       <c r="D165" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5766,25 +5763,25 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D166" t="n">
-        <v>90.5</v>
+        <v>318</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5794,30 +5791,29 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>7</v>
       </c>
       <c r="D167" t="n">
-        <v>170</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5827,29 +5823,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5859,30 +5855,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>7</v>
       </c>
       <c r="D169" t="n">
         <v>90.5</v>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5892,29 +5887,29 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D170" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -5924,14 +5919,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>7</v>
       </c>
       <c r="D171" t="n">
-        <v>128.7</v>
+        <v>170</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
@@ -5941,7 +5936,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -5956,14 +5951,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D172" t="n">
-        <v>128.7</v>
+        <v>90.5</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
@@ -5973,7 +5968,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -5988,14 +5983,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D173" t="n">
-        <v>257.9</v>
+        <v>90.5</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
@@ -6005,7 +6000,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6020,14 +6015,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>7</v>
       </c>
       <c r="D174" t="n">
-        <v>257.9</v>
+        <v>110</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
@@ -6037,7 +6032,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6052,14 +6047,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C175" t="n">
         <v>7</v>
       </c>
       <c r="D175" t="n">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
@@ -6069,7 +6064,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -6084,14 +6079,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>7</v>
       </c>
       <c r="D176" t="n">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
@@ -6101,7 +6096,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -6123,7 +6118,7 @@
         <v>7</v>
       </c>
       <c r="D177" t="n">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
@@ -6133,7 +6128,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -6155,17 +6150,17 @@
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>90.5</v>
+        <v>110</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -6187,17 +6182,17 @@
         <v>7</v>
       </c>
       <c r="D179" t="n">
-        <v>90.5</v>
+        <v>110</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6229,7 +6224,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6261,7 +6256,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6343,13 +6338,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C184" t="n">
-        <v>7</v>
-      </c>
       <c r="D184" t="n">
         <v>90.5</v>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6357,7 +6353,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -6372,16 +6368,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D185" t="n">
         <v>90.5</v>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6389,7 +6386,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -6404,14 +6401,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D186" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -6421,7 +6418,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6440,10 +6437,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D187" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
@@ -6453,7 +6450,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -6471,21 +6468,22 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C188" t="n">
-        <v>7</v>
-      </c>
       <c r="D188" t="n">
         <v>90.5</v>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -6500,24 +6498,25 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D189" t="n">
         <v>90.5</v>
       </c>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -6532,14 +6531,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D190" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
@@ -6549,7 +6548,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -6568,10 +6567,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D191" t="n">
-        <v>170</v>
+        <v>90.5</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
@@ -6581,7 +6580,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6599,13 +6598,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C192" t="n">
-        <v>6</v>
-      </c>
       <c r="D192" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E192" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6628,16 +6628,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>6</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D193" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E193" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F193" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6645,7 +6646,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6660,17 +6661,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>8</v>
       </c>
       <c r="D194" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D195" t="n">
-        <v>90.5</v>
+        <v>170</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
@@ -6728,27 +6728,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C196" t="n">
+        <v>16</v>
+      </c>
       <c r="D196" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6762,25 +6761,25 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D197" t="n">
-        <v>90.5</v>
+        <v>150</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6793,27 +6792,26 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C198" t="n">
+        <v>16</v>
+      </c>
       <c r="D198" t="n">
-        <v>170</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>187.5</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6827,25 +6825,25 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D199" t="n">
-        <v>170</v>
+        <v>187.5</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6860,7 @@
         <v>16</v>
       </c>
       <c r="D200" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
@@ -6872,7 +6870,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -6894,7 +6892,7 @@
         <v>16</v>
       </c>
       <c r="D201" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -6904,7 +6902,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -6926,17 +6924,17 @@
         <v>16</v>
       </c>
       <c r="D202" t="n">
-        <v>187.5</v>
+        <v>300</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -6958,17 +6956,17 @@
         <v>16</v>
       </c>
       <c r="D203" t="n">
-        <v>187.5</v>
+        <v>300</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -6990,7 +6988,7 @@
         <v>16</v>
       </c>
       <c r="D204" t="n">
-        <v>150</v>
+        <v>157.5</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
@@ -7022,7 +7020,7 @@
         <v>16</v>
       </c>
       <c r="D205" t="n">
-        <v>150</v>
+        <v>157.5</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
@@ -7051,20 +7049,20 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D206" t="n">
-        <v>157.5</v>
+        <v>70</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -7083,20 +7081,20 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D207" t="n">
-        <v>157.5</v>
+        <v>70</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -7115,10 +7113,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D208" t="n">
-        <v>120</v>
+        <v>604</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
@@ -7128,7 +7126,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7147,10 +7145,10 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D209" t="n">
-        <v>120</v>
+        <v>604</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
@@ -7160,7 +7158,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7175,14 +7173,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
-        <v>38</v>
+        <v>450</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
@@ -7192,7 +7190,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -7211,10 +7209,10 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D211" t="n">
-        <v>38</v>
+        <v>450</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
@@ -7224,7 +7222,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -7243,20 +7241,20 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D212" t="n">
-        <v>343</v>
+        <v>164.5</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -7275,20 +7273,20 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D213" t="n">
-        <v>343</v>
+        <v>164.5</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -7303,24 +7301,24 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D214" t="n">
-        <v>450</v>
+        <v>197</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -7339,20 +7337,20 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D215" t="n">
-        <v>450</v>
+        <v>197</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -7374,12 +7372,12 @@
         <v>7</v>
       </c>
       <c r="D216" t="n">
-        <v>164.5</v>
+        <v>197</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7406,12 +7404,12 @@
         <v>7</v>
       </c>
       <c r="D217" t="n">
-        <v>164.5</v>
+        <v>197</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7438,7 +7436,7 @@
         <v>7</v>
       </c>
       <c r="D218" t="n">
-        <v>197</v>
+        <v>164.5</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -7470,7 +7468,7 @@
         <v>7</v>
       </c>
       <c r="D219" t="n">
-        <v>197</v>
+        <v>164.5</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
@@ -7484,134 +7482,6 @@
         </is>
       </c>
       <c r="H219" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
-        <v>219</v>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
-        <v>7</v>
-      </c>
-      <c r="D220" t="n">
-        <v>197</v>
-      </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>p143</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>220</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
-        <v>7</v>
-      </c>
-      <c r="D221" t="n">
-        <v>197</v>
-      </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>p143</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>221</v>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Above</t>
-        </is>
-      </c>
-      <c r="C222" t="n">
-        <v>7</v>
-      </c>
-      <c r="D222" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>222</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
-        <v>7</v>
-      </c>
-      <c r="D223" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>CO009</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>p144</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
         <is>
           <t>CO009</t>
         </is>

--- a/焊缝统计_auto.xlsx
+++ b/焊缝统计_auto.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2484,7 +2484,7 @@
         <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>60</v>
+        <v>156.5</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2509,14 +2509,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>60</v>
+        <v>156.5</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>156.5</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2580,7 +2580,7 @@
         <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>15</v>
+        <v>156.5</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2617,12 +2617,12 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2649,12 +2649,12 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -2669,24 +2669,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2708,17 +2708,17 @@
         <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BE021</t>
+          <t>p122</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>p122</t>
+          <t>p123</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4224,7 +4224,7 @@
         <v>7</v>
       </c>
       <c r="D118" t="n">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
@@ -4256,7 +4256,7 @@
         <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
@@ -4288,17 +4288,17 @@
         <v>7</v>
       </c>
       <c r="D120" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
           <t>p42</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>p43</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4320,17 +4320,17 @@
         <v>7</v>
       </c>
       <c r="D121" t="n">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
           <t>p42</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>p43</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4352,17 +4352,17 @@
         <v>7</v>
       </c>
       <c r="D122" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
           <t>p42</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>p43</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -4384,17 +4384,17 @@
         <v>7</v>
       </c>
       <c r="D123" t="n">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
+          <t>BE023</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
           <t>p42</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>p43</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>6</v>
       </c>
       <c r="D124" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
@@ -4448,7 +4448,7 @@
         <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4477,25 +4477,25 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4509,25 +4509,25 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4541,25 +4541,25 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>268</v>
+        <v>150</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4573,25 +4573,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>268</v>
+        <v>150</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4605,25 +4605,25 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D131" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4669,25 +4669,25 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D132" t="n">
-        <v>90.5</v>
+        <v>232</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4701,25 +4701,25 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D133" t="n">
-        <v>90.5</v>
+        <v>232</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4729,29 +4729,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D134" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4761,29 +4761,29 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D135" t="n">
-        <v>90.5</v>
+        <v>150</v>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
     </row>
@@ -4793,14 +4793,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>7</v>
       </c>
       <c r="D136" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C138" t="n">
         <v>7</v>
       </c>
       <c r="D138" t="n">
-        <v>170</v>
+        <v>134.4</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>90.5</v>
+        <v>134.4</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>7</v>
       </c>
       <c r="D140" t="n">
-        <v>90.5</v>
+        <v>268</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>60</v>
+        <v>268</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -4985,24 +4985,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C142" t="n">
         <v>7</v>
       </c>
       <c r="D142" t="n">
-        <v>60</v>
+        <v>90.5</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -5029,12 +5029,12 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5049,24 +5049,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C144" t="n">
         <v>7</v>
       </c>
       <c r="D144" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D145" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D146" t="n">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>7</v>
       </c>
       <c r="D147" t="n">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>7</v>
       </c>
       <c r="D148" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>p127</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D149" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D150" t="n">
-        <v>116</v>
+        <v>90.5</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5273,17 +5273,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>7</v>
       </c>
       <c r="D151" t="n">
-        <v>116</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5309,14 +5308,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C152" t="n">
+        <v>7</v>
+      </c>
       <c r="D152" t="n">
-        <v>116</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5324,7 +5322,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5343,10 +5341,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D153" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
@@ -5356,7 +5354,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5371,14 +5369,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D154" t="n">
-        <v>116</v>
+        <v>90.5</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
@@ -5388,7 +5386,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5403,17 +5401,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>7</v>
       </c>
       <c r="D155" t="n">
-        <v>220</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5421,7 +5418,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -5439,14 +5436,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C156" t="n">
+        <v>7</v>
+      </c>
       <c r="D156" t="n">
-        <v>220</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5454,7 +5450,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5476,7 +5472,7 @@
         <v>7</v>
       </c>
       <c r="D157" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
@@ -5486,7 +5482,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5501,24 +5497,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C158" t="n">
         <v>7</v>
       </c>
       <c r="D158" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -5533,25 +5529,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>7</v>
       </c>
       <c r="D159" t="n">
-        <v>116</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -5569,14 +5564,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C160" t="n">
+        <v>9</v>
+      </c>
       <c r="D160" t="n">
         <v>116</v>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>CO007</t>
@@ -5584,7 +5578,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -5616,7 +5610,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -5631,14 +5625,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
@@ -5648,7 +5642,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -5663,29 +5657,29 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C163" t="n">
         <v>7</v>
       </c>
       <c r="D163" t="n">
-        <v>268</v>
+        <v>50</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p127</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5695,29 +5689,29 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D164" t="n">
-        <v>268</v>
+        <v>116</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5731,25 +5725,25 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D165" t="n">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5762,26 +5756,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C166" t="n">
-        <v>7</v>
-      </c>
       <c r="D166" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E166" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5791,29 +5786,30 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D167" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="E167" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5823,29 +5819,29 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D168" t="n">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5859,25 +5855,25 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D169" t="n">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>p101</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5890,26 +5886,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v>9</v>
-      </c>
       <c r="D170" t="n">
-        <v>116</v>
-      </c>
-      <c r="E170" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5919,29 +5916,30 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D171" t="n">
-        <v>116</v>
-      </c>
-      <c r="E171" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5951,29 +5949,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C172" t="n">
         <v>7</v>
       </c>
       <c r="D172" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -5990,22 +5988,22 @@
         <v>7</v>
       </c>
       <c r="D173" t="n">
-        <v>90.5</v>
+        <v>220</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6018,26 +6016,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>7</v>
-      </c>
       <c r="D174" t="n">
-        <v>60</v>
-      </c>
-      <c r="E174" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6047,29 +6046,30 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D175" t="n">
-        <v>60</v>
-      </c>
-      <c r="E175" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6079,29 +6079,29 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D176" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6115,25 +6115,25 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D177" t="n">
-        <v>90.5</v>
+        <v>116</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>p102</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>p126</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -6182,7 +6182,7 @@
         <v>7</v>
       </c>
       <c r="D179" t="n">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D180" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D181" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>p125</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6274,14 +6274,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C182" t="n">
+        <v>7</v>
+      </c>
       <c r="D182" t="n">
-        <v>116</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6289,7 +6288,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6304,17 +6303,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>7</v>
       </c>
       <c r="D183" t="n">
-        <v>116</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6322,7 +6320,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6337,14 +6335,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D184" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
@@ -6354,7 +6352,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -6373,10 +6371,10 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D185" t="n">
-        <v>116</v>
+        <v>250</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
@@ -6386,7 +6384,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -6404,14 +6402,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C186" t="n">
+        <v>7</v>
+      </c>
       <c r="D186" t="n">
-        <v>116</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6419,7 +6416,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6434,17 +6431,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>7</v>
       </c>
       <c r="D187" t="n">
-        <v>116</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>90.5</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6452,7 +6448,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -6467,14 +6463,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
@@ -6484,7 +6480,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -6503,10 +6499,10 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
@@ -6516,7 +6512,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p101</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -6534,14 +6530,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C190" t="n">
+        <v>9</v>
+      </c>
       <c r="D190" t="n">
-        <v>220</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6549,7 +6544,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -6564,17 +6559,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>9</v>
       </c>
       <c r="D191" t="n">
-        <v>220</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>CO008</t>
@@ -6582,7 +6576,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -6597,14 +6591,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C192" t="n">
         <v>7</v>
       </c>
       <c r="D192" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
@@ -6614,7 +6608,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -6636,7 +6630,7 @@
         <v>7</v>
       </c>
       <c r="D193" t="n">
-        <v>220</v>
+        <v>90.5</v>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
@@ -6646,7 +6640,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>p124</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -6665,25 +6659,25 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D194" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6697,25 +6691,25 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D195" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6729,25 +6723,25 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>187.5</v>
+        <v>90.5</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6761,25 +6755,25 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D197" t="n">
-        <v>187.5</v>
+        <v>90.5</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p102</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p126</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6793,25 +6787,25 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D198" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6825,25 +6819,25 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D199" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6857,25 +6851,25 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D200" t="n">
-        <v>157.5</v>
+        <v>116</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6889,25 +6883,25 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D201" t="n">
-        <v>157.5</v>
+        <v>116</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p125</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6920,26 +6914,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C202" t="n">
-        <v>16</v>
-      </c>
       <c r="D202" t="n">
-        <v>120</v>
-      </c>
-      <c r="E202" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6949,29 +6944,30 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>16</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D203" t="n">
-        <v>120</v>
-      </c>
-      <c r="E203" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -6981,29 +6977,29 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D204" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7017,25 +7013,25 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D205" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>p17</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7048,26 +7044,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C206" t="n">
-        <v>10</v>
-      </c>
       <c r="D206" t="n">
-        <v>604</v>
-      </c>
-      <c r="E206" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7077,29 +7074,30 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>10</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D207" t="n">
-        <v>604</v>
-      </c>
-      <c r="E207" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7113,25 +7111,25 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D208" t="n">
-        <v>450</v>
+        <v>116</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7145,25 +7143,25 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D209" t="n">
-        <v>450</v>
+        <v>116</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>p7</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7176,26 +7174,27 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C210" t="n">
-        <v>7</v>
-      </c>
       <c r="D210" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E210" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7205,29 +7204,30 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D211" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="E211" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7237,29 +7237,29 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C212" t="n">
         <v>7</v>
       </c>
       <c r="D212" t="n">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7276,22 +7276,22 @@
         <v>7</v>
       </c>
       <c r="D213" t="n">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>p143</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>p144</t>
+          <t>p124</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
     </row>
@@ -7305,25 +7305,25 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D214" t="n">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7333,29 +7333,29 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D215" t="n">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7369,25 +7369,25 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D216" t="n">
-        <v>216</v>
+        <v>187.5</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7401,25 +7401,25 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D217" t="n">
-        <v>216</v>
+        <v>187.5</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7429,29 +7429,29 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D218" t="n">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7465,25 +7465,25 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D219" t="n">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>p195</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7493,29 +7493,29 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D220" t="n">
-        <v>208</v>
+        <v>157.5</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7525,29 +7525,29 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D221" t="n">
-        <v>207</v>
+        <v>157.5</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7557,29 +7557,29 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D222" t="n">
-        <v>207</v>
+        <v>120</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7589,29 +7589,29 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D223" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7621,29 +7621,29 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D224" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7653,29 +7653,29 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D225" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p17</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7685,29 +7685,29 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D226" t="n">
-        <v>109</v>
+        <v>604</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>p199</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7717,29 +7717,29 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D227" t="n">
-        <v>78.59999999999999</v>
+        <v>604</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7749,29 +7749,29 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D228" t="n">
-        <v>78.59999999999999</v>
+        <v>450</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7785,25 +7785,25 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D229" t="n">
-        <v>73.3</v>
+        <v>450</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7817,25 +7817,25 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D230" t="n">
-        <v>73.3</v>
+        <v>450</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7845,29 +7845,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D231" t="n">
-        <v>92.7</v>
+        <v>450</v>
       </c>
       <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p7</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7877,29 +7877,29 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D232" t="n">
-        <v>92.7</v>
+        <v>190</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7909,29 +7909,29 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D233" t="n">
-        <v>78.59999999999999</v>
+        <v>190</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7941,29 +7941,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D234" t="n">
-        <v>78.59999999999999</v>
+        <v>222</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -7973,29 +7973,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D235" t="n">
-        <v>73.3</v>
+        <v>222</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p143</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8005,29 +8005,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D236" t="n">
-        <v>73.3</v>
+        <v>190</v>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8037,29 +8037,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D237" t="n">
-        <v>92.7</v>
+        <v>190</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p144</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
     </row>
@@ -8069,14 +8069,14 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D238" t="n">
-        <v>92.7</v>
+        <v>216</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D239" t="n">
-        <v>78.59999999999999</v>
+        <v>216</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -8133,14 +8133,14 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D240" t="n">
-        <v>78.59999999999999</v>
+        <v>216</v>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -8165,14 +8165,14 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D241" t="n">
-        <v>73.3</v>
+        <v>216</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D242" t="n">
-        <v>73.3</v>
+        <v>216</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D243" t="n">
-        <v>92.7</v>
+        <v>216</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p195</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D244" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -8293,17 +8293,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>10</v>
       </c>
       <c r="D245" t="n">
-        <v>90</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8311,7 +8310,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -8329,14 +8328,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C246" t="n">
+        <v>7</v>
+      </c>
       <c r="D246" t="n">
-        <v>90</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8344,7 +8342,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -8359,17 +8357,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>7</v>
       </c>
       <c r="D247" t="n">
-        <v>90</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8377,7 +8374,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -8392,14 +8389,14 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D248" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
@@ -8409,7 +8406,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -8428,10 +8425,10 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D249" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
@@ -8441,7 +8438,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -8456,14 +8453,14 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D250" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
@@ -8473,7 +8470,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -8488,14 +8485,14 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D251" t="n">
-        <v>58.7</v>
+        <v>109</v>
       </c>
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
@@ -8505,7 +8502,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p199</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -8527,7 +8524,7 @@
         <v>12</v>
       </c>
       <c r="D252" t="n">
-        <v>58.7</v>
+        <v>120.5</v>
       </c>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
@@ -8537,7 +8534,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -8552,14 +8549,14 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C253" t="n">
         <v>12</v>
       </c>
       <c r="D253" t="n">
-        <v>58.7</v>
+        <v>120.5</v>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
@@ -8569,7 +8566,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -8584,14 +8581,14 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C254" t="n">
         <v>12</v>
       </c>
       <c r="D254" t="n">
-        <v>58.7</v>
+        <v>15.3</v>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
@@ -8601,7 +8598,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -8623,7 +8620,7 @@
         <v>12</v>
       </c>
       <c r="D255" t="n">
-        <v>58.7</v>
+        <v>15.3</v>
       </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
@@ -8633,7 +8630,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -8648,14 +8645,14 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C256" t="n">
         <v>12</v>
       </c>
       <c r="D256" t="n">
-        <v>58.7</v>
+        <v>92.7</v>
       </c>
       <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
@@ -8665,7 +8662,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -8680,17 +8677,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>12</v>
       </c>
       <c r="D257" t="n">
         <v>92.7</v>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8698,7 +8694,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -8716,14 +8712,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C258" t="n">
+        <v>12</v>
+      </c>
       <c r="D258" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>199.3</v>
+      </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8731,7 +8726,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -8746,17 +8741,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>12</v>
       </c>
       <c r="D259" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>199.3</v>
+      </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8764,7 +8758,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -8782,14 +8776,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C260" t="n">
+        <v>12</v>
+      </c>
       <c r="D260" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8797,7 +8790,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -8812,17 +8805,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>12</v>
       </c>
       <c r="D261" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8830,7 +8822,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -8845,14 +8837,14 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D262" t="n">
-        <v>92.7</v>
+        <v>26.2</v>
       </c>
       <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
@@ -8862,7 +8854,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -8881,10 +8873,10 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D263" t="n">
-        <v>92.7</v>
+        <v>26.2</v>
       </c>
       <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
@@ -8894,7 +8886,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -8909,16 +8901,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C264" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D264" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E264" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8926,7 +8919,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -8941,16 +8934,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C265" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D265" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E265" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F265" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8958,7 +8952,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -8973,16 +8967,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C266" t="n">
-        <v>7</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D266" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E266" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F266" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -8990,7 +8985,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>p202</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -9005,14 +9000,14 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D267" t="n">
-        <v>58.7</v>
+        <v>90</v>
       </c>
       <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
@@ -9022,7 +9017,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -9037,14 +9032,14 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D268" t="n">
-        <v>58.7</v>
+        <v>90</v>
       </c>
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
@@ -9054,7 +9049,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -9069,14 +9064,14 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D269" t="n">
-        <v>58.7</v>
+        <v>90</v>
       </c>
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
@@ -9086,7 +9081,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -9101,7 +9096,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -9118,7 +9113,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -9133,7 +9128,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -9150,7 +9145,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -9165,7 +9160,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -9182,7 +9177,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>p194</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -9197,14 +9192,14 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C273" t="n">
         <v>12</v>
       </c>
       <c r="D273" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
@@ -9214,7 +9209,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -9236,7 +9231,7 @@
         <v>12</v>
       </c>
       <c r="D274" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
@@ -9246,7 +9241,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -9261,17 +9256,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>12</v>
       </c>
       <c r="D275" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>58.7</v>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9279,7 +9273,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -9294,16 +9288,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C276" t="n">
-        <v>8</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D276" t="n">
-        <v>233.3</v>
-      </c>
-      <c r="E276" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9311,7 +9306,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>p183</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -9329,13 +9324,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C277" t="n">
-        <v>9</v>
-      </c>
       <c r="D277" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="E277" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9343,7 +9339,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -9358,16 +9354,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D278" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="E278" t="inlineStr"/>
+        <v>92.7</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9375,7 +9372,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -9393,13 +9390,14 @@
           <t>Above</t>
         </is>
       </c>
-      <c r="C279" t="n">
-        <v>9</v>
-      </c>
       <c r="D279" t="n">
         <v>92.7</v>
       </c>
-      <c r="E279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9407,7 +9405,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -9422,16 +9420,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C280" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D280" t="n">
         <v>92.7</v>
       </c>
-      <c r="E280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9439,7 +9438,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -9454,14 +9453,14 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D281" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
@@ -9471,7 +9470,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -9490,10 +9489,10 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D282" t="n">
-        <v>73.3</v>
+        <v>92.7</v>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
@@ -9503,7 +9502,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -9518,14 +9517,14 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D283" t="n">
-        <v>106.7</v>
+        <v>92.7</v>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
@@ -9535,7 +9534,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -9554,10 +9553,10 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D284" t="n">
-        <v>106.7</v>
+        <v>92.7</v>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
@@ -9567,7 +9566,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -9582,11 +9581,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D285" t="n">
         <v>92.7</v>
@@ -9599,7 +9598,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p202</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -9614,14 +9613,14 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D286" t="n">
-        <v>92.7</v>
+        <v>58.7</v>
       </c>
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
@@ -9631,7 +9630,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -9650,10 +9649,10 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D287" t="n">
-        <v>73.3</v>
+        <v>58.7</v>
       </c>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
@@ -9663,7 +9662,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -9678,14 +9677,14 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D288" t="n">
-        <v>73.3</v>
+        <v>58.7</v>
       </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
@@ -9695,7 +9694,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -9710,14 +9709,14 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D289" t="n">
-        <v>106.7</v>
+        <v>58.7</v>
       </c>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
@@ -9727,7 +9726,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -9746,10 +9745,10 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D290" t="n">
-        <v>106.7</v>
+        <v>58.7</v>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
@@ -9759,7 +9758,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -9774,14 +9773,14 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D291" t="n">
-        <v>92.7</v>
+        <v>58.7</v>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
@@ -9791,7 +9790,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p194</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -9806,14 +9805,14 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D292" t="n">
-        <v>92.7</v>
+        <v>60</v>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
@@ -9823,7 +9822,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>p185</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -9838,14 +9837,14 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Above</t>
+          <t>Below</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D293" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
@@ -9855,7 +9854,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -9870,16 +9869,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Below</t>
-        </is>
-      </c>
-      <c r="C294" t="n">
-        <v>9</v>
+          <t>Above</t>
+        </is>
       </c>
       <c r="D294" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E294" t="inlineStr"/>
+        <v>233.3</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -9902,17 +9902,16 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>8</v>
       </c>
       <c r="D295" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>233.3</v>
+      </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9920,7 +9919,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p183</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -9938,14 +9937,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C296" t="n">
+        <v>9</v>
+      </c>
       <c r="D296" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>233.3</v>
+      </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9953,7 +9951,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -9968,17 +9966,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>9</v>
       </c>
       <c r="D297" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>233.3</v>
+      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -9986,7 +9983,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -10001,14 +9998,14 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D298" t="n">
-        <v>73.3</v>
+        <v>112.7</v>
       </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
@@ -10018,7 +10015,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -10037,10 +10034,10 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D299" t="n">
-        <v>73.3</v>
+        <v>112.7</v>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
@@ -10050,7 +10047,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -10065,14 +10062,14 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D300" t="n">
-        <v>73.3</v>
+        <v>233.3</v>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
@@ -10082,7 +10079,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -10097,17 +10094,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>9</v>
       </c>
       <c r="D301" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>233.3</v>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10115,7 +10111,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -10133,14 +10129,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C302" t="n">
+        <v>9</v>
+      </c>
       <c r="D302" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>112.7</v>
+      </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10148,7 +10143,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -10163,17 +10158,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>9</v>
       </c>
       <c r="D303" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>112.7</v>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10181,7 +10175,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -10196,14 +10190,14 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D304" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
@@ -10213,7 +10207,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -10232,10 +10226,10 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D305" t="n">
-        <v>92.7</v>
+        <v>208</v>
       </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
@@ -10245,7 +10239,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -10260,11 +10254,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D306" t="n">
         <v>92.7</v>
@@ -10277,7 +10271,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -10292,17 +10286,16 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>9</v>
       </c>
       <c r="D307" t="n">
         <v>92.7</v>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10310,7 +10303,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -10328,14 +10321,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C308" t="n">
+        <v>9</v>
+      </c>
       <c r="D308" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>206.7</v>
+      </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10343,7 +10335,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -10358,17 +10350,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>9</v>
       </c>
       <c r="D309" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>206.7</v>
+      </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10376,7 +10367,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -10391,14 +10382,14 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D310" t="n">
-        <v>92.7</v>
+        <v>173.3</v>
       </c>
       <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
@@ -10408,7 +10399,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -10427,10 +10418,10 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D311" t="n">
-        <v>92.7</v>
+        <v>173.3</v>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
@@ -10440,7 +10431,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>p197</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -10455,14 +10446,14 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D312" t="n">
-        <v>92.7</v>
+        <v>233.3</v>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
@@ -10472,7 +10463,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>p198</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -10487,17 +10478,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>9</v>
       </c>
       <c r="D313" t="n">
-        <v>200</v>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>233.3</v>
+      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10505,7 +10495,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -10523,14 +10513,13 @@
           <t>Above</t>
         </is>
       </c>
+      <c r="C314" t="n">
+        <v>9</v>
+      </c>
       <c r="D314" t="n">
-        <v>200</v>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>112.7</v>
+      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10538,7 +10527,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -10553,17 +10542,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Above</t>
-        </is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>9</v>
       </c>
       <c r="D315" t="n">
-        <v>200</v>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>CJP</t>
-        </is>
-      </c>
+        <v>112.7</v>
+      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>CO010</t>
@@ -10571,7 +10559,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>p185</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -10586,14 +10574,14 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D316" t="n">
-        <v>200</v>
+        <v>233.3</v>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
@@ -10603,7 +10591,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -10622,10 +10610,10 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D317" t="n">
-        <v>200</v>
+        <v>233.3</v>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
@@ -10635,7 +10623,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>p197</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -10650,14 +10638,14 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Below</t>
+          <t>Above</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D318" t="n">
-        <v>200</v>
+        <v>112.7</v>
       </c>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
@@ -10667,10 +10655,1590 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>9</v>
+      </c>
+      <c r="D319" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>9</v>
+      </c>
+      <c r="D320" t="n">
+        <v>208</v>
+      </c>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>9</v>
+      </c>
+      <c r="D321" t="n">
+        <v>208</v>
+      </c>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>9</v>
+      </c>
+      <c r="D322" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
           <t>p197</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>9</v>
+      </c>
+      <c r="D323" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>9</v>
+      </c>
+      <c r="D324" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>9</v>
+      </c>
+      <c r="D325" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>9</v>
+      </c>
+      <c r="D326" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>9</v>
+      </c>
+      <c r="D327" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>9</v>
+      </c>
+      <c r="D328" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>9</v>
+      </c>
+      <c r="D329" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>9</v>
+      </c>
+      <c r="D330" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>9</v>
+      </c>
+      <c r="D331" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>p185</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>9</v>
+      </c>
+      <c r="D332" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>9</v>
+      </c>
+      <c r="D333" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>9</v>
+      </c>
+      <c r="D334" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>9</v>
+      </c>
+      <c r="D335" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>9</v>
+      </c>
+      <c r="D336" t="n">
+        <v>208</v>
+      </c>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>9</v>
+      </c>
+      <c r="D337" t="n">
+        <v>208</v>
+      </c>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>9</v>
+      </c>
+      <c r="D338" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>9</v>
+      </c>
+      <c r="D339" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>9</v>
+      </c>
+      <c r="D340" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>9</v>
+      </c>
+      <c r="D341" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>9</v>
+      </c>
+      <c r="D342" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>9</v>
+      </c>
+      <c r="D343" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>7</v>
+      </c>
+      <c r="D347" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>7</v>
+      </c>
+      <c r="D348" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>7</v>
+      </c>
+      <c r="D349" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>7</v>
+      </c>
+      <c r="D353" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>7</v>
+      </c>
+      <c r="D354" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>7</v>
+      </c>
+      <c r="D355" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>7</v>
+      </c>
+      <c r="D359" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>7</v>
+      </c>
+      <c r="D360" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>7</v>
+      </c>
+      <c r="D361" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>p198</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>200</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>200</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Above</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>200</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>CJP</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>8</v>
+      </c>
+      <c r="D365" t="n">
+        <v>200</v>
+      </c>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>8</v>
+      </c>
+      <c r="D366" t="n">
+        <v>200</v>
+      </c>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Below</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>8</v>
+      </c>
+      <c r="D367" t="n">
+        <v>200</v>
+      </c>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>CO010</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>p197</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
         <is>
           <t>CO010</t>
         </is>
